--- a/conv_details_pandas.xlsx
+++ b/conv_details_pandas.xlsx
@@ -358,7 +358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -379,22 +379,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>suspectedCount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>curedCount</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>deadCount</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>locationId</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>cityEnglishName</t>
         </is>
       </c>
     </row>
@@ -414,15 +409,14 @@
         <v>183</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>16</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -440,15 +434,14 @@
         <v>111</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>107</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -466,18 +459,13 @@
         <v>22</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>19</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>310113</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Baoshan District</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -496,18 +484,13 @@
         <v>9</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>310114</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Jiading District</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -526,18 +509,13 @@
         <v>61</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>60</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>310115</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Pudong District</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -556,18 +534,13 @@
         <v>19</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>19</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
       <c r="G7" t="n">
-        <v>310112</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Minhang District</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -586,18 +559,13 @@
         <v>18</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>17</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>310104</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Xuhui District</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -616,18 +584,13 @@
         <v>16</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>15</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>310106</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Jing'an District</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -646,18 +609,13 @@
         <v>14</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>14</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
-        <v>310117</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Songjiang District</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -676,18 +634,13 @@
         <v>13</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>13</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
-        <v>310105</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Changning District</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -706,18 +659,13 @@
         <v>11</v>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>11</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
-        <v>310107</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Putuo District</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -736,18 +684,13 @@
         <v>9</v>
       </c>
       <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>9</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
-        <v>310110</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Yangpu District</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -766,18 +709,13 @@
         <v>9</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>9</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
-        <v>310120</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Fengxian District</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -796,18 +734,13 @@
         <v>7</v>
       </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>7</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
-        <v>310109</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Hongkou District</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -826,18 +759,13 @@
         <v>6</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>6</v>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
-        <v>310101</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Huangpu District</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -856,18 +784,13 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>6</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
-        <v>310118</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Qingpu District</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -886,18 +809,13 @@
         <v>4</v>
       </c>
       <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>4</v>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
-        <v>310116</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Jinshan District</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -916,18 +834,13 @@
         <v>4</v>
       </c>
       <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>4</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
-        <v>310151</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Chongming District</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -949,21 +862,16 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Area not defined</t>
-        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>汇总</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -974,18 +882,19 @@
         <v>522</v>
       </c>
       <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>343</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>6</v>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>平均值</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -996,18 +905,19 @@
         <v>27.47368421052632</v>
       </c>
       <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
         <v>18.05263157894737</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>0.3157894736842105</v>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>中位数</t>
+          <t>Median</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1018,13 +928,14 @@
         <v>11</v>
       </c>
       <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
         <v>11</v>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
